--- a/docs/reference-forms/output/xlsx/TAI-FORM-REF-C011.xlsx
+++ b/docs/reference-forms/output/xlsx/TAI-FORM-REF-C011.xlsx
@@ -10,8 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="도급·용역·위탁 업체 안전보건 수준 평가" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'도급·용역·위탁 업체 안전보건 수준 평가'!$A$2:$D$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'도급·용역·위탁 업체 안전보건 수준 평가'!$A$1:$D$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'도급·용역·위탁 업체 안전보건 수준 평가'!$A$1:$D$276</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +35,12 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
@@ -45,20 +50,8 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <i val="1"/>
-      <color rgb="00000000"/>
-      <sz val="8"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -72,22 +65,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FAFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FAFAFA"/>
+        <fgColor rgb="00DCE6F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,25 +97,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -203,6 +185,19 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_REF_C011_1" displayName="T_REF_C011_1" ref="A15:D75" headerRowCount="1">
+  <autoFilter ref="A15:D75"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="평가항목"/>
+    <tableColumn id="2" name="배점"/>
+    <tableColumn id="3" name="점수"/>
+    <tableColumn id="4" name="비고"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -494,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.3" customWidth="1" min="1" max="1"/>
@@ -510,199 +505,500 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>평가항목 및 기준 (총 100점)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>I. 안전보건관리체계 (40점): 도급·용역·위탁받는 자의 안전보건관리 체계 구축 수준</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1-1. 리더십 (10점): 경영방침, 인력·시설·장비 등 자원 배정의 적정성 등</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1-2. 근로자 참여 (10점): 종사자 의견수렴 절차 및 이행 적정성</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1-3. 위험요인 파악 및 제거·대체·통제 (10점): 위험요인 파악 및 개선절차 및 수준의 적정성</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1-4. 비상조치계획 (10점): 비상조치계획 적정성</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>II. 도급·용역·위탁 안전보건 관리계획 (60점): 도급·용역·위탁받는 업무에 대한 안전보건관리계획 적정성</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2-1. 위험요인 파악 및 제거·대체·통제 (15점): 도급·용역·위탁받는 업무에 대한 위험요인 파악, 제거·대체 및 통제 방법의 적정성(위험성평가 및 대책의 적정성)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2-2. 자원 배정(시설·장비) (15점): 도급·용역·위탁받는 업무의 위험요인 관리에 적합한 시설·장비 배정 및 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       사용 기계·기구 및 설비의 종류 및 관리계획</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2-3. 자원 배정(인력) (15점): 도급·용역·위탁받는 업무의 위험요인 관리에 적합한 인력 배정 및 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       도급·용역·위탁받는 업무 관련 실적, 작업자 이력·자격·경력 현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2-4. 비상조치계획 (15점): 도급·용역·위탁받는 업무 시 발생 가능한 비상상황 및 대처에 적합한 비상조치계획</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>평가항목</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>배점</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>점수</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="3" t="inlineStr"/>
-      <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr"/>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="3">
-        <f>SUM(C3:C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>평가항목 및 기준 (총 100점)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>I. 안전보건관리체계 (40점): 도급·용역·위탁받는 자의 안전보건관리 체계 구축 수준</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1-1. 리더십 (10점): 경영방침, 인력·시설·장비 등 자원 배정의 적정성 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1-2. 근로자 참여 (10점): 종사자 의견수렴 절차 및 이행 적정성</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1-3. 위험요인 파악 및 제거·대체·통제 (10점): 위험요인 파악 및 개선절차 및 수준의 적정성</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1-4. 비상조치계획 (10점): 비상조치계획 적정성</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>II. 도급·용역·위탁 안전보건 관리계획 (60점): 도급·용역·위탁받는 업무에 대한 안전보건관리계획 적정성</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2-1. 위험요인 파악 및 제거·대체·통제 (15점): 도급·용역·위탁받는 업무에 대한 위험요인 파악, 제거·대체 및 통제 방법의 적정성(위험성평가 및 대책의 적정성)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2-2. 자원 배정(시설·장비) (15점): 도급·용역·위탁받는 업무의 위험요인 관리에 적합한 시설·장비 배정 및 운영</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       사용 기계·기구 및 설비의 종류 및 관리계획</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2-3. 자원 배정(인력) (15점): 도급·용역·위탁받는 업무의 위험요인 관리에 적합한 인력 배정 및 운영</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       도급·용역·위탁받는 업무 관련 실적, 작업자 이력·자격·경력 현황</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2-4. 비상조치계획 (15점): 도급·용역·위탁받는 업무 시 발생 가능한 비상상황 및 대처에 적합한 비상조치계획</t>
-        </is>
-      </c>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="4" t="inlineStr"/>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr"/>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="4" t="inlineStr"/>
+      <c r="B21" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr"/>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="4" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr"/>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="4" t="inlineStr"/>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="4" t="inlineStr"/>
+      <c r="B25" s="4" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="4" t="inlineStr"/>
+      <c r="B26" s="4" t="inlineStr"/>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="4" t="inlineStr"/>
+      <c r="B27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="4" t="inlineStr"/>
+      <c r="B28" s="4" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="4" t="inlineStr"/>
+      <c r="B29" s="4" t="inlineStr"/>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="4" t="inlineStr"/>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="4" t="inlineStr"/>
+      <c r="B31" s="4" t="inlineStr"/>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="4" t="inlineStr"/>
+      <c r="B32" s="4" t="inlineStr"/>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="4" t="inlineStr"/>
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="4" t="inlineStr"/>
+      <c r="B34" s="4" t="inlineStr"/>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="4" t="inlineStr"/>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="4" t="inlineStr"/>
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="4" t="inlineStr"/>
+      <c r="B37" s="4" t="inlineStr"/>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="4" t="inlineStr"/>
+      <c r="B38" s="4" t="inlineStr"/>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="4" t="inlineStr"/>
+      <c r="B39" s="4" t="inlineStr"/>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="4" t="inlineStr"/>
+      <c r="B40" s="4" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="4" t="inlineStr"/>
+      <c r="B41" s="4" t="inlineStr"/>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="4" t="inlineStr"/>
+      <c r="B42" s="4" t="inlineStr"/>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="4" t="inlineStr"/>
+      <c r="B43" s="4" t="inlineStr"/>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="4" t="inlineStr"/>
+      <c r="B44" s="4" t="inlineStr"/>
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="4" t="inlineStr"/>
+      <c r="B45" s="4" t="inlineStr"/>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="4" t="inlineStr"/>
+      <c r="B46" s="4" t="inlineStr"/>
+      <c r="C46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="4" t="inlineStr"/>
+      <c r="B47" s="4" t="inlineStr"/>
+      <c r="C47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="4" t="inlineStr"/>
+      <c r="B48" s="4" t="inlineStr"/>
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="4" t="inlineStr"/>
+      <c r="B49" s="4" t="inlineStr"/>
+      <c r="C49" s="4" t="inlineStr"/>
+      <c r="D49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="4" t="inlineStr"/>
+      <c r="B50" s="4" t="inlineStr"/>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="4" t="inlineStr"/>
+      <c r="B51" s="4" t="inlineStr"/>
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="4" t="inlineStr"/>
+      <c r="B52" s="4" t="inlineStr"/>
+      <c r="C52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="4" t="inlineStr"/>
+      <c r="B53" s="4" t="inlineStr"/>
+      <c r="C53" s="4" t="inlineStr"/>
+      <c r="D53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="4" t="inlineStr"/>
+      <c r="B54" s="4" t="inlineStr"/>
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="4" t="inlineStr"/>
+      <c r="B55" s="4" t="inlineStr"/>
+      <c r="C55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="4" t="inlineStr"/>
+      <c r="B56" s="4" t="inlineStr"/>
+      <c r="C56" s="4" t="inlineStr"/>
+      <c r="D56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="4" t="inlineStr"/>
+      <c r="B57" s="4" t="inlineStr"/>
+      <c r="C57" s="4" t="inlineStr"/>
+      <c r="D57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="4" t="inlineStr"/>
+      <c r="B58" s="4" t="inlineStr"/>
+      <c r="C58" s="4" t="inlineStr"/>
+      <c r="D58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="4" t="inlineStr"/>
+      <c r="B59" s="4" t="inlineStr"/>
+      <c r="C59" s="4" t="inlineStr"/>
+      <c r="D59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="4" t="inlineStr"/>
+      <c r="B60" s="4" t="inlineStr"/>
+      <c r="C60" s="4" t="inlineStr"/>
+      <c r="D60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="4" t="inlineStr"/>
+      <c r="B61" s="4" t="inlineStr"/>
+      <c r="C61" s="4" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="4" t="inlineStr"/>
+      <c r="B62" s="4" t="inlineStr"/>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="4" t="inlineStr"/>
+      <c r="B63" s="4" t="inlineStr"/>
+      <c r="C63" s="4" t="inlineStr"/>
+      <c r="D63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="4" t="inlineStr"/>
+      <c r="B64" s="4" t="inlineStr"/>
+      <c r="C64" s="4" t="inlineStr"/>
+      <c r="D64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="4" t="inlineStr"/>
+      <c r="B65" s="4" t="inlineStr"/>
+      <c r="C65" s="4" t="inlineStr"/>
+      <c r="D65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="4" t="inlineStr"/>
+      <c r="B66" s="4" t="inlineStr"/>
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="4" t="inlineStr"/>
+      <c r="B67" s="4" t="inlineStr"/>
+      <c r="C67" s="4" t="inlineStr"/>
+      <c r="D67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="4" t="inlineStr"/>
+      <c r="B68" s="4" t="inlineStr"/>
+      <c r="C68" s="4" t="inlineStr"/>
+      <c r="D68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="4" t="inlineStr"/>
+      <c r="B69" s="4" t="inlineStr"/>
+      <c r="C69" s="4" t="inlineStr"/>
+      <c r="D69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="4" t="inlineStr"/>
+      <c r="B70" s="4" t="inlineStr"/>
+      <c r="C70" s="4" t="inlineStr"/>
+      <c r="D70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="4" t="inlineStr"/>
+      <c r="B71" s="4" t="inlineStr"/>
+      <c r="C71" s="4" t="inlineStr"/>
+      <c r="D71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="4" t="inlineStr"/>
+      <c r="B72" s="4" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr"/>
+      <c r="D72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="4" t="inlineStr"/>
+      <c r="B73" s="4" t="inlineStr"/>
+      <c r="C73" s="4" t="inlineStr"/>
+      <c r="D73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="4" t="inlineStr"/>
+      <c r="B74" s="4" t="inlineStr"/>
+      <c r="C74" s="4" t="inlineStr"/>
+      <c r="D74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="4" t="inlineStr"/>
+      <c r="B75" s="4" t="inlineStr"/>
+      <c r="C75" s="4" t="inlineStr"/>
+      <c r="D75" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D10"/>
   <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/docs/reference-forms/output/xlsx/TAI-FORM-REF-C011.xlsx
+++ b/docs/reference-forms/output/xlsx/TAI-FORM-REF-C011.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="도급·용역·위탁 업체 안전보건 수준 평가" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'도급·용역·위탁 업체 안전보건 수준 평가'!$A$1:$D$276</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'도급·용역·위탁 업체 안전보건 수준 평가'!$A$1:$D$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
